--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B2" t="n">
-        <v>74705</v>
+        <v>78598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R2" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>74705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,37 +803,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R3" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R2" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B3" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R3" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +906,7 @@
         <v>121270553</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B2" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R2" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,37 +803,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R3" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>74710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R2" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B3" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R3" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +906,7 @@
         <v>121270553</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B2" t="n">
-        <v>74710</v>
+        <v>78607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R2" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,37 +803,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R3" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +906,7 @@
         <v>121270553</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B2" t="n">
-        <v>78607</v>
+        <v>74713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R2" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B3" t="n">
-        <v>74713</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R3" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B2" t="n">
-        <v>74713</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R2" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>74714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,37 +803,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R3" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +906,7 @@
         <v>121270553</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121266163</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121266553</v>
       </c>
       <c r="B3" t="n">
-        <v>74714</v>
+        <v>74715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>121270553</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45991-2024 artfynd.xlsx
+++ b/artfynd/A 45991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121266163</v>
+        <v>121266553</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518180</v>
+        <v>518142</v>
       </c>
       <c r="R2" t="n">
-        <v>6993769</v>
+        <v>6993712</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121266553</v>
+        <v>121266163</v>
       </c>
       <c r="B3" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,40 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åselmyren, Åselmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518142</v>
+        <v>518180</v>
       </c>
       <c r="R3" t="n">
-        <v>6993712</v>
+        <v>6993769</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
